--- a/output/Python/o3-mini-high/task_analysis_results_singlepass_Python_o3-mini-high_zebralogic.xlsx
+++ b/output/Python/o3-mini-high/task_analysis_results_singlepass_Python_o3-mini-high_zebralogic.xlsx
@@ -1506,110 +1506,94 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Wrong plan</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="inlineStr">
-        <is>
-          <t>{"solution": {"header": ["House", "Name", "Hobby", "Height", "Lunch"], "rows": [["1", "Peter", "knitting", "short", "spaghetti"], ["2", "Eric", "painting", "very tall", "stew"], ["3", "Bob", "photography", "tall", "grilled cheese"], ["4", "Alice", "cooking", "average", "stir fry"], ["5", "Arnold", "gardening", "very short", "pizza"]]}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-6x6-20</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G3" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "favorite cigar",
-      "favorite music",
-      "favorite drink",
-      "mothers' names",
-      "lunch"
+      "Hobby",
+      "Height",
+      "Food"
     ],
     "rows": [
       [
         "1",
+        "Peter",
+        "knitting",
+        "short",
+        "spaghetti"
+      ],
+      [
+        "2",
         "Eric",
-        "dunhill",
-        "country",
-        "tea",
-        "Aniya",
-        "spaghetti"
-      ],
-      [
-        "2",
-        "Carol",
-        "prince",
-        "rock",
-        "water",
-        "Penny",
+        "painting",
+        "very tall",
         "stew"
       ],
       [
         "3",
+        "Bob",
+        "photography",
+        "tall",
+        "grilled cheese"
+      ],
+      [
+        "4",
         "Alice",
-        "blue master",
-        "hip hop",
-        "boba tea",
-        "Sarah",
-        "grilled cheese"
-      ],
-      [
-        "4",
-        "Peter",
-        "blends",
-        "jazz",
-        "root beer",
-        "Kailyn",
+        "cooking",
+        "average",
         "stir fry"
       ],
       [
         "5",
         "Arnold",
-        "pall mall",
-        "pop",
-        "milk",
-        "Janelle",
+        "gardening",
+        "very short",
         "pizza"
-      ],
-      [
-        "6",
-        "Bob",
-        "yellow monster",
-        "classical",
-        "coffee",
-        "Holly</t>
+      ]
+    ]
+  }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-6x6-20</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="b">
+        <v>0</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Cigar", "MusicGenre", "Drink", "Mother", "Food"], "rows": [["1", "Eric", "dunhill", "country", "tea", "Aniya", "spaghetti"], ["2", "Carol", "prince", "rock", "water", "Penny", "stew"], ["3", "Alice", "blue master", "hip hop", "boba tea", "Sarah", "grilled cheese"], ["4", "Peter", "blends", "jazz", "root beer", "Kailyn", "stir fry"], ["5", "Arnold", "pall mall", "pop", "milk", "Janelle", "pizza"], ["6", "Bob", "yellow monster", "classical", "coffee", "Holly", "soup"]]}}</t>
         </is>
       </c>
     </row>
@@ -1627,27 +1611,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Wrong plan</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">{
+          <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "phone model",
-      "favorite cigar",
-      "favorite flower",
-      "favorite color",
-      "favorite sport"
+      "PhoneModel",
+      "Cigar",
+      "Flower",
+      "Color",
+      "FavoriteSport"
     ],
     "rows": [
       [
@@ -1699,7 +1683,8 @@
         "6",
         "Bob",
         "google pixel 6",
-       </t>
+        "pall mall",
+        "tulips</t>
         </is>
       </c>
     </row>
@@ -1717,55 +1702,90 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Wrong plan</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Flower", "HairColor", "FavoriteSport", "HouseStyle", "Pet"], "rows": [["1", "Arnold", "carnations", "brown", "tennis", "victorian", "fish"], ["2", "Peter", "daffodils", "blonde", "basketball", "ranch", "dog"], ["3", "Eric", "lilies", "black", "soccer", "colonial", "cat"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-6x3-39</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "Favorite flower",
-      "Hair color",
-      "Favorite sport",
-      "House style",
-      "Pet"
+      "Children",
+      "Smoothie"
     ],
     "rows": [
       [
         "1",
         "Arnold",
-        "carnations",
-        "brown",
-        "tennis",
-        "victorian",
-        "fish"
+        "Bella",
+        "blueberry"
       ],
       [
         "2",
-        "Peter",
-        "daffodils",
-        "blonde",
-        "basketball",
-        "ranch",
-        "dog"
+        "Carol",
+        "Fred",
+        "cherry"
       ],
       [
         "3",
         "Eric",
-        "lilies",
-        "black",
-        "soccer",
-        "colonial",
-        "cat"
+        "Samantha",
+        "desert"
+      ],
+      [
+        "4",
+        "Alice",
+        "Alice",
+        "watermelon"
+      ],
+      [
+        "5",
+        "Bob",
+        "Timothy",
+        "lime"
+      ],
+      [
+        "6",
+        "Peter",
+        "Meredith",
+        "dragonfruit"
       ]
     ]
   }
@@ -1773,35 +1793,6 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-6x3-39</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="b">
-        <v>0</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Correct</t>
-        </is>
-      </c>
-      <c r="E6" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>{"solution": {"header": ["House", "Name", "child", "smoothie"], "rows": [["1", "Arnold", "Bella", "blueberry"], ["2", "Carol", "Fred", "cherry"], ["3", "Eric", "Samantha", "desert"], ["4", "Alice", "Alice", "watermelon"], ["5", "Bob", "Timothy", "lime"], ["6", "Peter", "Meredith", "dragonfruit"]]}}</t>
-        </is>
-      </c>
-    </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -1816,18 +1807,18 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Wrong plan</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>{"solution": {"header": ["House", "Name", "hobby", "favorite book genres", "favorite music genres", "birthday month"], "rows": [["1", "Eric", "gardening", "mystery", "rock", "sept"], ["2", "Arnold", "photography", "science fiction", "pop", "april"]]}}</t>
+          <t>{"solution": {"header": ["House", "Name", "Hobby", "BookGenre", "MusicGenre", "Birthday"], "rows": [["1", "Eric", "gardening", "mystery", "rock", "sept"], ["2", "Arnold", "photography", "science fiction", "pop", "april"]]}}</t>
         </is>
       </c>
     </row>
@@ -1849,14 +1840,14 @@
         </is>
       </c>
       <c r="E8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>{"solution": {"header": ["House", "Name", "flower", "height", "mother", "occupation", "sport"], "rows": [["1", "Arnold", "lilies", "tall", "Kailyn", "teacher", "tennis"], ["2", "Peter", "carnations", "average", "Janelle", "doctor", "basketball"], ["3", "Eric", "roses", "very short", "Holly", "engineer", "swimming"], ["4", "Alice", "daffodils", "short", "Aniya", "artist", "soccer"]]}}</t>
+          <t>{"solution": {"header": ["House", "Name", "Flower", "Height", "Mother", "Occupation", "FavoriteSport"], "rows": [["1", "Arnold", "lilies", "tall", "Kailyn", "teacher", "tennis"], ["2", "Peter", "carnations", "average", "Janelle", "doctor", "basketball"], ["3", "Eric", "roses", "very short", "Holly", "engineer", "swimming"], ["4", "Alice", "daffodils", "short", "Aniya", "artist", "soccer"]]}}</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1869,7 @@
         </is>
       </c>
       <c r="E9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -1890,7 +1881,7 @@
     "header": [
       "House",
       "Name",
-      "height"
+      "Height"
     ],
     "rows": [
       [
@@ -1928,18 +1919,18 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Wrong plan</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>{"solution": {"header": ["House", "Name", "pet", "style", "birthday"], "rows": [["1", "Bob", "cat", "mediterranean", "feb"], ["2", "Peter", "rabbit", "colonial", "may"], ["3", "Carol", "bird", "victorian", "mar"], ["4", "Arnold", "dog", "craftsman", "jan"], ["5", "Alice", "fish", "modern", "april"], ["6", "Eric", "hamster", "ranch", "sept"]]}}</t>
+          <t>{"solution": {"header": ["House", "Name", "Pet", "HouseStyle", "Birthday"], "rows": [["1", "Bob", "cat", "mediterranean", "feb"], ["2", "Peter", "rabbit", "colonial", "may"], ["3", "Carol", "bird", "victorian", "mar"], ["4", "Arnold", "dog", "craftsman", "jan"], ["5", "Alice", "fish", "modern", "april"], ["6", "Eric", "hamster", "ranch", "sept"]]}}</t>
         </is>
       </c>
     </row>
@@ -1967,74 +1958,39 @@
         <v>1</v>
       </c>
       <c r="G11" t="inlineStr">
-        <is>
-          <t>{"solution": {"header": ["House", "Name", "Height"], "rows": [["1", "Eric", "very tall"], ["2", "Peter", "short"], ["3", "Bob", "very short"], ["4", "Alice", "tall"], ["5", "Arnold", "average"]]}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-5x3-18</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Correct</t>
-        </is>
-      </c>
-      <c r="E12" t="b">
-        <v>0</v>
-      </c>
-      <c r="F12" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "favorite flower",
-      "animal"
+      "Height"
     ],
     "rows": [
       [
         "1",
+        "Eric",
+        "very tall"
+      ],
+      [
+        "2",
+        "Peter",
+        "short"
+      ],
+      [
+        "3",
+        "Bob",
+        "very short"
+      ],
+      [
+        "4",
+        "Alice",
+        "tall"
+      ],
+      [
+        "5",
         "Arnold",
-        "lilies",
-        "bird"
-      ],
-      [
-        "2",
-        "Alice",
-        "carnations",
-        "dog"
-      ],
-      [
-        "3",
-        "Eric",
-        "tulips",
-        "horse"
-      ],
-      [
-        "4",
-        "Peter",
-        "daffodils",
-        "fish"
-      ],
-      [
-        "5",
-        "Bob",
-        "roses",
-        "cat"
+        "average"
       ]
     ]
   }
@@ -2042,6 +1998,35 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-5x3-18</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Flower", "Animal"], "rows": [["1", "Arnold", "lilies", "bird"], ["2", "Alice", "carnations", "dog"], ["3", "Eric", "tulips", "horse"], ["4", "Peter", "daffodils", "fish"], ["5", "Bob", "roses", "cat"]]}}</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
@@ -2056,197 +2041,400 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Wrong plan</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="inlineStr">
-        <is>
-          <t>{"solution": {"header": ["House", "Name", "vacation", "education", "favorite color", "phone", "lunch"], "rows": [["1", "Eric", "camping", "doctorate", "blue", "iphone 13", "pizza"], ["2", "Bob", "mountain", "bachelor", "white", "huawei p50", "stir fry"], ["3", "Eric", "city", "doctorate", "yellow", "samsung galaxy s21", "pizza"], ["4", "Alice", "cruise", "master", "green", "oneplus 9", "spaghetti"], ["5", "Arnold", "beach", "high school", "red", "google pixel 6", "grilled cheese"]]}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-4x5-0</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="b">
-        <v>0</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Correct</t>
-        </is>
-      </c>
-      <c r="E14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F14" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>{"solution": {"header": ["House", "Name", "Smoothie", "Cigar", "Height", "Phone"], "rows": [["1", "Eric", "dragonfruit", "pall mall", "average", "samsung galaxy s21"], ["2", "Peter", "desert", "blue master", "very short", "iphone 13"], ["3", "Alice", "watermelon", "prince", "tall", "oneplus 9"], ["4", "Arnold", "cherry", "dunhill", "short", "google pixel 6"]]}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-4x2-21</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="b">
-        <v>0</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E15" t="b">
-        <v>0</v>
-      </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>{"solution": {"header": ["House", "Name", "House style"], "rows": [["1", "Eric", "ranch"], ["2", "Alice", "craftsman"], ["3", "Arnold", "victorian"], ["4", "Peter", "colonial"]]}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-3x3-6</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="b">
-        <v>0</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E16" t="b">
-        <v>0</v>
-      </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>{"solution": {"header": ["House", "Name", "Book genre", "Vacation"], "rows": [["1", "Eric", "mystery", "mountain"], ["2", "Arnold", "science fiction", "beach"], ["3", "Peter", "romance", "city"]]}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-6x5-8</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="b">
-        <v>0</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E17" t="b">
-        <v>0</v>
-      </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>{"solution": {"header": ["House", "Name", "Animal", "Occupation", "Favorite Sport", "Height"], "rows": []}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-5x5-39</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="b">
-        <v>0</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Correct</t>
-        </is>
-      </c>
-      <c r="E18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F18" t="b">
-        <v>1</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>{"solution": {"header": ["House", "Name", "birthday", "mother", "occupation", "hair"], "rows": [["1", "Eric", "feb", "Penny", "doctor", "red"], ["2", "Peter", "sept", "Holly", "lawyer", "black"], ["3", "Arnold", "april", "Janelle", "engineer", "blonde"], ["4", "Bob", "jan", "Aniya", "artist", "brown"], ["5", "Alice", "mar", "Kailyn", "teacher", "gray"]]}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-3x2-10</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="b">
-        <v>0</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Correct</t>
-        </is>
-      </c>
-      <c r="E19" t="b">
-        <v>0</v>
-      </c>
-      <c r="F19" t="b">
-        <v>1</v>
-      </c>
-      <c r="G19" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "height"
+      "Vacation",
+      "Education",
+      "Color",
+      "PhoneModel",
+      "Food"
+    ],
+    "rows": [
+      [
+        "1",
+        "Peter",
+        "camping",
+        "high school",
+        "white",
+        "iphone 13",
+        "spaghetti"
+      ],
+      [
+        "2",
+        "Bob",
+        "mountain",
+        "bachelor",
+        "blue",
+        "huawei p50",
+        "stir fry"
+      ],
+      [
+        "3",
+        "Eric",
+        "city",
+        "doctorate",
+        "yellow",
+        "samsung galaxy s21",
+        "pizza"
+      ],
+      [
+        "4",
+        "Alice",
+        "cruise",
+        "master",
+        "green",
+        "oneplus 9",
+        "stew"
+      ],
+      [
+        "5",
+        "Arnold",
+        "beach",
+        "associate",
+        "red",
+        "google pixel 6",
+        "grilled cheese"
+      ]
+    ]
+  }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-4x5-0</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Wrong plan</t>
+        </is>
+      </c>
+      <c r="E14" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Smoothie", "Cigar", "Height", "PhoneModel"], "rows": [["1", "Eric", "dragonfruit", "pall mall", "average", "samsung galaxy s21"], ["2", "Peter", "desert", "blue master", "very short", "iphone 13"], ["3", "Alice", "watermelon", "prince", "tall", "oneplus 9"], ["4", "Arnold", "cherry", "dunhill", "short", "google pixel 6"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-4x2-21</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E15" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "HouseStyle"
+    ],
+    "rows": [
+      [
+        "1",
+        "Eric",
+        "ranch"
+      ],
+      [
+        "2",
+        "Alice",
+        "craftsman"
+      ],
+      [
+        "3",
+        "Arnold",
+        "victorian"
+      ],
+      [
+        "4",
+        "Peter",
+        "colonial"
+      ]
+    ]
+  }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-3x3-6</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "BookGenre", "Vacation"], "rows": [["1", "Eric", "mystery", "mountain"], ["2", "Arnold", "science fiction", "beach"], ["3", "Peter", "romance", "city"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-6x5-8</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "Animal",
+      "Occupation",
+      "FavoriteSport",
+      "Height"
+    ],
+    "rows": [
+      [
+        "1",
+        "Peter",
+        "bird",
+        "nurse",
+        "baseball",
+        "very tall"
+      ],
+      [
+        "2",
+        "Eric",
+        "dog",
+        "engineer",
+        "swimming",
+        "average"
+      ],
+      [
+        "3",
+        "Alice",
+        "rabbit",
+        "artist",
+        "volleyball",
+        "tall"
+      ],
+      [
+        "4",
+        "Bob",
+        "horse",
+        "teacher",
+        "tennis",
+        "very short"
+      ],
+      [
+        "5",
+        "Carol",
+        "fish",
+        "lawyer",
+        "soccer",
+        "super tall"
+      ],
+      [
+        "6",
+        "Arnold",
+        "cat",
+        "doctor",
+        "basketball",
+        "short"
+      ]
+    ]
+  }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-5x5-39</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E18" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "Birthday",
+      "Mother",
+      "Occupation",
+      "HairColor"
+    ],
+    "rows": [
+      [
+        "1",
+        "Eric",
+        "feb",
+        "Penny",
+        "doctor",
+        "red"
+      ],
+      [
+        "2",
+        "Peter",
+        "sept",
+        "Holly",
+        "lawyer",
+        "black"
+      ],
+      [
+        "3",
+        "Arnold",
+        "april",
+        "Janelle",
+        "engineer",
+        "blonde"
+      ],
+      [
+        "4",
+        "Bob",
+        "jan",
+        "Aniya",
+        "artist",
+        "brown"
+      ],
+      [
+        "5",
+        "Alice",
+        "mar",
+        "Kailyn",
+        "teacher",
+        "gray"
+      ]
+    ]
+  }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-3x2-10</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E19" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "Height"
     ],
     "rows": [
       [
@@ -2383,86 +2571,56 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Wrong plan</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "HairColor"], "rows": [["1", "Alice", "red"], ["2", "Arnold", "black"], ["3", "Eric", "brown"], ["4", "Peter", "blonde"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-3x6-29</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E23" t="b">
+        <v>1</v>
+      </c>
+      <c r="F23" t="b">
+        <v>1</v>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "Hair Color"
-    ],
-    "rows": [
-      [
-        "1",
-        "Alice",
-        "red"
-      ],
-      [
-        "2",
-        "Arnold",
-        "black"
-      ],
-      [
-        "3",
-        "Eric",
-        "brown"
-      ],
-      [
-        "4",
-        "Peter",
-        "blonde"
-      ]
-    ]
-  }
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-3x6-29</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" t="b">
-        <v>0</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Correct</t>
-        </is>
-      </c>
-      <c r="E23" t="b">
-        <v>0</v>
-      </c>
-      <c r="F23" t="b">
-        <v>1</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>{
-  "solution": {
-    "header": [
-      "House",
-      "Name",
-      "animal",
-      "birthday",
-      "hobby",
-      "drink",
-      "hair"
+      "Animal",
+      "Birthday",
+      "Hobby",
+      "Drink",
+      "HairColor"
     ],
     "rows": [
       [
@@ -2512,142 +2670,55 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Wrong plan</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="inlineStr">
-        <is>
-          <t>{"solution": {"header": ["House", "Name", "Drink", "Vacation", "House Style", "Animal", "Birthday"], "rows": [["1", "Arnold", "tea", "beach", "colonial", "bird", "sept"], ["2", "Peter", "milk", "city", "ranch", "horse", "jan"], ["3", "Eric", "water", "mountain", "victorian", "cat", "april"]]}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-3x6-16</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" t="b">
-        <v>0</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E25" t="b">
-        <v>0</v>
-      </c>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>{"solution": {"header": ["House", "Name", "favorite drink", "nationality", "level of education", "style of house", "favorite smoothie"], "rows": [["1", "Eric", "milk", "dane", "high school", "ranch", "watermelon"], ["2", "Peter", "water", "swede", "bachelor", "victorian", "desert"], ["3", "Arnold", "tea", "brit", "associate", "colonial", "cherry"]]}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-6x3-13</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E26" t="b">
-        <v>0</v>
-      </c>
-      <c r="F26" t="b">
-        <v>0</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>{"solution": {"header": ["House", "Name", "book genre", "occupation"], "rows": [["1", "Carol", "mystery", "doctor"], ["2", "Bob", "science fiction", "artist"], ["3", "Eric", "historical fiction", "nurse"], ["4", "Alice", "fantasy", "lawyer"], ["5", "Arnold", "biography", "teacher"], ["6", "Peter", "romance", "engineer"]]}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-3x6-9</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" t="b">
-        <v>0</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E27" t="b">
-        <v>0</v>
-      </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
-      <c r="G27" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "Car",
-      "House style",
-      "Pet",
-      "Occupation",
-      "Vacation"
+      "Drink",
+      "Vacation",
+      "HouseStyle",
+      "Animal",
+      "Birthday"
     ],
     "rows": [
       [
         "1",
-        "Eric",
-        "tesla model 3",
-        "ranch",
-        "fish",
-        "doctor",
-        "city"
+        "Arnold",
+        "tea",
+        "beach",
+        "colonial",
+        "bird",
+        "sept"
       ],
       [
         "2",
         "Peter",
-        "toyota camry",
+        "milk",
+        "city",
+        "ranch",
+        "horse",
+        "jan"
+      ],
+      [
+        "3",
+        "Eric",
+        "water",
+        "mountain",
         "victorian",
-        "dog",
-        "engineer",
-        "beach"
-      ],
-      [
-        "3",
-        "Arnold",
-        "ford f150",
-        "colonial",
         "cat",
-        "teacher",
-        "mountain"
+        "april"
       ]
     ]
   }
@@ -2655,145 +2726,69 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-3x6-35</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" t="b">
-        <v>0</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E28" t="b">
-        <v>0</v>
-      </c>
-      <c r="F28" t="b">
-        <v>0</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>{"solution": {"header": ["House", "Name", "vacation", "height", "favorite flower", "hair color", "education"], "rows": [["1", "Eric", "beach", "very short", "lilies", "brown", "bachelor"], ["2", "Peter", "mountain", "average", "carnations", "black", "associate"], ["3", "Arnold", "city", "short", "daffodils", "blonde", "high school"]]}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-3x3-0</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" t="b">
-        <v>0</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Correct</t>
-        </is>
-      </c>
-      <c r="E29" t="b">
-        <v>1</v>
-      </c>
-      <c r="F29" t="b">
-        <v>1</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>{"solution": {"header": ["House", "Name", "Education", "Occupation"], "rows": [["1", "Peter", "high school", "teacher"], ["2", "Arnold", "associate", "engineer"], ["3", "Eric", "bachelor", "doctor"]]}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-5x6-8</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" t="b">
-        <v>0</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E30" t="b">
-        <v>0</v>
-      </c>
-      <c r="F30" t="b">
-        <v>0</v>
-      </c>
-      <c r="G30" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-3x6-16</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E25" t="b">
+        <v>1</v>
+      </c>
+      <c r="F25" t="b">
+        <v>1</v>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "style",
-      "mother",
-      "phone",
-      "drink",
-      "animal"
+      "Drink",
+      "Nationality",
+      "Education",
+      "HouseStyle",
+      "Smoothie"
     ],
     "rows": [
       [
         "1",
+        "Eric",
+        "milk",
+        "dane",
+        "high school",
+        "ranch",
+        "watermelon"
+      ],
+      [
+        "2",
         "Peter",
+        "water",
+        "swede",
+        "bachelor",
         "victorian",
-        "Aniya",
-        "huawei p50",
-        "root beer",
-        "cat"
-      ],
-      [
-        "2",
+        "desert"
+      ],
+      [
+        "3",
         "Arnold",
-        "ranch",
-        "Kailyn",
-        "iphone 13",
-        "milk",
-        "dog"
-      ],
-      [
-        "3",
-        "Eric",
-        "modern",
-        "Penny",
-        "oneplus 9",
-        "coffee",
-        "horse"
-      ],
-      [
-        "4",
-        "Bob",
-        "craftsman",
-        "Holly",
-        "google pixel 6",
         "tea",
-        "bird"
-      ],
-      [
-        "5",
-        "Alice",
+        "brit",
+        "associate",
         "colonial",
-        "Janelle",
-        "samsung galaxy s21",
-        "water",
-        "fish"
+        "cherry"
       ]
     ]
   }
@@ -2801,82 +2796,75 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-6x4-32</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" t="b">
-        <v>0</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E31" t="b">
-        <v>0</v>
-      </c>
-      <c r="F31" t="b">
-        <v>0</v>
-      </c>
-      <c r="G31" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-6x3-13</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="b">
+        <v>0</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E26" t="b">
+        <v>1</v>
+      </c>
+      <c r="F26" t="b">
+        <v>1</v>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "House Style",
-      "Favorite Music Genre",
-      "Hobby"
+      "BookGenre",
+      "Occupation"
     ],
     "rows": [
       [
         "1",
+        "Carol",
+        "mystery",
+        "doctor"
+      ],
+      [
+        "2",
+        "Bob",
+        "science fiction",
+        "artist"
+      ],
+      [
+        "3",
+        "Eric",
+        "historical fiction",
+        "nurse"
+      ],
+      [
+        "4",
+        "Alice",
+        "fantasy",
+        "lawyer"
+      ],
+      [
+        "5",
         "Arnold",
-        "craftsman",
-        "country",
-        "painting"
-      ],
-      [
-        "2",
-        "Carol",
-        "mediterranean",
-        "hip hop",
-        "cooking"
-      ],
-      [
-        "3",
-        "Bob",
-        "colonial",
-        "classical",
-        "knitting"
-      ],
-      [
-        "4",
+        "biography",
+        "teacher"
+      ],
+      [
+        "6",
         "Peter",
-        "victorian",
-        "jazz",
-        "woodworking"
-      ],
-      [
-        "5",
-        "Eric",
-        "ranch",
-        "rock",
-        "gardening"
-      ],
-      [
-        "6",
-        "Alice",
-        "modern",
-        "pop",
-        "photography"
+        "romance",
+        "engineer"
       ]
     ]
   }
@@ -2884,6 +2872,160 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-3x6-9</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="b">
+        <v>0</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E27" t="b">
+        <v>1</v>
+      </c>
+      <c r="F27" t="b">
+        <v>1</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "CarModel", "HouseStyle", "Pet", "Occupation", "Vacation"], "rows": [["1", "Eric", "tesla model 3", "ranch", "fish", "doctor", "city"], ["2", "Peter", "toyota camry", "victorian", "dog", "engineer", "beach"], ["3", "Arnold", "ford f150", "colonial", "cat", "teacher", "mountain"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-3x6-35</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="b">
+        <v>0</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E28" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Vacation", "Height", "Flower", "HairColor", "Education"], "rows": [["1", "Eric", "beach", "very short", "lilies", "brown", "bachelor"], ["2", "Peter", "mountain", "average", "carnations", "black", "associate"], ["3", "Arnold", "city", "short", "daffodils", "blonde", "high school"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-3x3-0</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="b">
+        <v>1</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E29" t="b">
+        <v>0</v>
+      </c>
+      <c r="F29" t="b">
+        <v>0</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Traceback (most recent call last):
+  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 00:29:05.py", line 85, in &lt;module&gt;
+    main()
+  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 00:29:05.py", line 11, in main
+    for name_perm in itertools.permutations(names):
+                     ^^^^^^^^^
+NameError: name 'itertools' is not defined. Did you forget to import 'itertools'?</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-5x6-8</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="b">
+        <v>0</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E30" t="b">
+        <v>1</v>
+      </c>
+      <c r="F30" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "HouseStyle", "Mother", "PhoneModel", "Drink", "Animal"], "rows": [["1", "Peter", "victorian", "Aniya", "huawei p50", "root beer", "cat"], ["2", "Arnold", "ranch", "Kailyn", "iphone 13", "milk", "dog"], ["3", "Eric", "modern", "Penny", "oneplus 9", "coffee", "horse"], ["4", "Bob", "craftsman", "Holly", "google pixel 6", "tea", "bird"], ["5", "Alice", "colonial", "Janelle", "samsung galaxy s21", "water", "fish"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-6x4-32</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="b">
+        <v>1</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E31" t="b">
+        <v>0</v>
+      </c>
+      <c r="F31" t="b">
+        <v>0</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 00:29:05.py", line 1
+    Check constraints that can be evaluated immediately when assigning a candidate
+          ^^^^^^^^^^^
+SyntaxError: invalid syntax</t>
+        </is>
+      </c>
+    </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -2898,464 +3040,16 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Wrong plan</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" t="inlineStr">
-        <is>
-          <t>{"solution": {"header": ["House", "Name", "Occupation", "Birthday Month", "House Style", "Height", "Favorite Cigar"], "rows": [["1", "Eric", "engineer", "april", "colonial", "very short", "prince"], ["2", "Arnold", "doctor", "sept", "victorian", "short", "pall mall"]]}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-2x5-23</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" t="b">
-        <v>0</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E33" t="b">
-        <v>0</v>
-      </c>
-      <c r="F33" t="b">
-        <v>0</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>{
-  "solution": {
-    "header": [
-      "House",
-      "Name",
-      "level of education",
-      "height",
-      "lunch",
-      "favorite drink"
-    ],
-    "rows": [
-      [
-        "1",
-        "Arnold",
-        "high school",
-        "very short",
-        "pizza",
-        "water"
-      ],
-      [
-        "2",
-        "Eric",
-        "associate",
-        "short",
-        "grilled cheese",
-        "tea"
-      ]
-    ]
-  }
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-2x4-11</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" t="b">
-        <v>0</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Correct</t>
-        </is>
-      </c>
-      <c r="E34" t="b">
-        <v>1</v>
-      </c>
-      <c r="F34" t="b">
-        <v>1</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>{"solution": {"header": ["House", "Name", "Hobby", "Pet", "Height"], "rows": [["1", "Eric", "photography", "dog", "very short"], ["2", "Arnold", "gardening", "cat", "short"]]}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-3x5-3</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" t="b">
-        <v>0</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Correct</t>
-        </is>
-      </c>
-      <c r="E35" t="b">
-        <v>1</v>
-      </c>
-      <c r="F35" t="b">
-        <v>1</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>{
-  "solution": {
-    "header": [
-      "House",
-      "Name",
-      "Smoothie",
-      "Flower",
-      "Animal",
-      "Hobby"
-    ],
-    "rows": [
-      [
-        "1",
-        "Arnold",
-        "desert",
-        "daffodils",
-        "cat",
-        "cooking"
-      ],
-      [
-        "2",
-        "Peter",
-        "watermelon",
-        "carnations",
-        "horse",
-        "gardening"
-      ],
-      [
-        "3",
-        "Eric",
-        "cherry",
-        "lilies",
-        "bird",
-        "photography"
-      ]
-    ]
-  }
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-2x4-30</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" t="b">
-        <v>0</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E36" t="b">
-        <v>0</v>
-      </c>
-      <c r="F36" t="b">
-        <v>0</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>{"solution": {"header": ["House", "Name", "Hair Color", "Favorite Sport", "Favorite Smoothie"], "rows": [["1", "Arnold", "brown", "basketball", "desert"], ["2", "Eric", "black", "soccer", "cherry"]]}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-4x2-8</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" t="b">
-        <v>0</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Correct</t>
-        </is>
-      </c>
-      <c r="E37" t="b">
-        <v>0</v>
-      </c>
-      <c r="F37" t="b">
-        <v>1</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>{
-  "solution": {
-    "header": [
-      "House",
-      "Name",
-      "favorite color"
-    ],
-    "rows": [
-      [
-        "1",
-        "Peter",
-        "white"
-      ],
-      [
-        "2",
-        "Alice",
-        "red"
-      ],
-      [
-        "3",
-        "Arnold",
-        "green"
-      ],
-      [
-        "4",
-        "Eric",
-        "yellow"
-      ]
-    ]
-  }
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-6x2-10</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" t="b">
-        <v>0</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E38" t="b">
-        <v>0</v>
-      </c>
-      <c r="F38" t="b">
-        <v>0</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>{"solution": {"header": ["House", "Name", "Favorite Music"], "rows": [["1", "Peter", "rock"], ["2", "Eric", "classical"], ["3", "Bob", "hip hop"], ["4", "Arnold", "pop"], ["5", "Alice", "jazz"], ["6", "Carol", "country"]]}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-4x3-8</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" t="b">
-        <v>0</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E39" t="b">
-        <v>0</v>
-      </c>
-      <c r="F39" t="b">
-        <v>0</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>{"solution": {"header": ["House", "Name", "hair color", "favorite music genre"], "rows": [["1", "Alice", "black", "classical"], ["2", "Arnold", "blonde", "rock"], ["3", "Eric", "red", "jazz"], ["4", "Peter", "brown", "pop"]]}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-3x4-22</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" t="b">
-        <v>0</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E40" t="b">
-        <v>0</v>
-      </c>
-      <c r="F40" t="b">
-        <v>0</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>{
-  "solution": {
-    "header": [
-      "House",
-      "Name",
-      "favorite music genres",
-      "child",
-      "favorite book genres"
-    ],
-    "rows": [
-      [
-        "1",
-        "Peter",
-        "pop",
-        "Fred",
-        "romance"
-      ],
-      [
-        "2",
-        "Eric",
-        "classical",
-        "Bella",
-        "mystery"
-      ],
-      [
-        "3",
-        "Arnold",
-        "rock",
-        "Meredith",
-        "science fiction"
-      ]
-    ]
-  }
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-5x5-29</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" t="b">
-        <v>0</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Correct</t>
-        </is>
-      </c>
-      <c r="E41" t="b">
-        <v>0</v>
-      </c>
-      <c r="F41" t="b">
-        <v>1</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>{"solution": {"header": ["House", "Name", "nationality", "vacation", "education", "occupation"], "rows": [["1", "Alice", "german", "beach", "doctorate", "doctor"], ["2", "Arnold", "norwegian", "cruise", "associate", "lawyer"], ["3", "Bob", "dane", "city", "bachelor", "engineer"], ["4", "Eric", "brit", "camping", "master", "teacher"], ["5", "Peter", "swede", "mountain", "high school", "artist"]]}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-6x4-9</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>1</v>
-      </c>
-      <c r="C42" t="b">
-        <v>0</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Correct</t>
-        </is>
-      </c>
-      <c r="E42" t="b">
-        <v>0</v>
-      </c>
-      <c r="F42" t="b">
-        <v>1</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>{"solution": {"header": ["House", "Name", "Phone", "Nationality", "Color"], "rows": [["1", "Carol", "xiaomi mi 11", "chinese", "green"], ["2", "Arnold", "oneplus 9", "norwegian", "purple"], ["3", "Alice", "google pixel 6", "german", "red"], ["4", "Eric", "huawei p50", "dane", "yellow"], ["5", "Bob", "samsung galaxy s21", "swede", "white"], ["6", "Peter", "iphone 13", "brit", "blue"]]}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-3x5-19</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>1</v>
-      </c>
-      <c r="C43" t="b">
-        <v>0</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Correct</t>
-        </is>
-      </c>
-      <c r="E43" t="b">
-        <v>1</v>
-      </c>
-      <c r="F43" t="b">
-        <v>1</v>
-      </c>
-      <c r="G43" t="inlineStr">
         <is>
           <t>{
   "solution": {
@@ -3363,34 +3057,29 @@
       "House",
       "Name",
       "Occupation",
-      "Education",
-      "Smoothie",
-      "Hobby"
+      "Birthday",
+      "HouseStyle",
+      "Height",
+      "Cigar"
     ],
     "rows": [
       [
         "1",
+        "Eric",
+        "engineer",
+        "april",
+        "colonial",
+        "very short",
+        "prince"
+      ],
+      [
+        "2",
         "Arnold",
-        "engineer",
-        "high school",
-        "watermelon",
-        "gardening"
-      ],
-      [
-        "2",
-        "Peter",
         "doctor",
-        "associate",
-        "desert",
-        "cooking"
-      ],
-      [
-        "3",
-        "Eric",
-        "teacher",
-        "bachelor",
-        "cherry",
-        "photography"
+        "sept",
+        "victorian",
+        "short",
+        "pall mall"
       ]
     ]
   }
@@ -3398,66 +3087,465 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-4x5-32</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>1</v>
-      </c>
-      <c r="C44" t="b">
-        <v>0</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Correct</t>
-        </is>
-      </c>
-      <c r="E44" t="b">
-        <v>0</v>
-      </c>
-      <c r="F44" t="b">
-        <v>1</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>{"solution": {"header": ["House", "Name", "Hobby", "Birthday Month", "Education", "Smoothie"], "rows": [["1", "Arnold", "photography", "april", "associate", "dragonfruit"], ["2", "Eric", "gardening", "jan", "bachelor", "desert"], ["3", "Alice", "cooking", "sept", "high school", "cherry"], ["4", "Peter", "painting", "feb", "master", "watermelon"]]}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-6x3-11</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>1</v>
-      </c>
-      <c r="C45" t="b">
-        <v>0</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Correct</t>
-        </is>
-      </c>
-      <c r="E45" t="b">
-        <v>0</v>
-      </c>
-      <c r="F45" t="b">
-        <v>1</v>
-      </c>
-      <c r="G45" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-2x5-23</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="b">
+        <v>0</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F33" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Education", "Height", "Food", "Drink"], "rows": [["1", "Arnold", "high school", "very short", "pizza", "water"], ["2", "Eric", "associate", "short", "grilled cheese", "tea"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-2x4-11</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="b">
+        <v>0</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E34" t="b">
+        <v>1</v>
+      </c>
+      <c r="F34" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Hobby", "Pet", "Height"], "rows": [["1", "Eric", "photography", "dog", "very short"], ["2", "Arnold", "gardening", "cat", "short"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-3x5-3</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="b">
+        <v>0</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E35" t="b">
+        <v>1</v>
+      </c>
+      <c r="F35" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Smoothie", "Flower", "Animal", "Hobby"], "rows": [["1", "Arnold", "desert", "daffodils", "cat", "cooking"], ["2", "Peter", "watermelon", "carnations", "horse", "gardening"], ["3", "Eric", "cherry", "lilies", "bird", "photography"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-2x4-30</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="b">
+        <v>0</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E36" t="b">
+        <v>1</v>
+      </c>
+      <c r="F36" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "Hair",
+      "HairColor",
+      "FavoriteSport",
+      "Smoothie"
+    ],
+    "rows": [
+      [
+        "1",
+        "Arnold",
+        "brown",
+        "basketball",
+        "desert"
+      ],
+      [
+        "2",
+        "Eric",
+        "black",
+        "soccer",
+        "cherry"
+      ]
+    ]
+  }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-4x2-8</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="b">
+        <v>0</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E37" t="b">
+        <v>1</v>
+      </c>
+      <c r="F37" t="b">
+        <v>1</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Color"], "rows": [["1", "Peter", "white"], ["2", "Alice", "red"], ["3", "Arnold", "green"], ["4", "Eric", "yellow"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-6x2-10</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="b">
+        <v>0</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E38" t="b">
+        <v>1</v>
+      </c>
+      <c r="F38" t="b">
+        <v>1</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "MusicGenre"], "rows": [["1", "Peter", "pop"], ["2", "Eric", "rock"], ["3", "Bob", "hip hop"], ["4", "Arnold", "jazz"], ["5", "Alice", "classical"], ["6", "Carol", "country"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-4x3-8</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="b">
+        <v>0</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E39" t="b">
+        <v>1</v>
+      </c>
+      <c r="F39" t="b">
+        <v>1</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "HairColor", "MusicGenre"], "rows": [["1", "Alice", "black", "classical"], ["2", "Arnold", "blonde", "rock"], ["3", "Eric", "red", "jazz"], ["4", "Peter", "brown", "pop"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-3x4-22</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="b">
+        <v>0</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E40" t="b">
+        <v>1</v>
+      </c>
+      <c r="F40" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "MusicGenre", "Children", "BookGenre"], "rows": [["1", "Peter", "pop", "Fred", "romance"], ["2", "Eric", "classical", "Bella", "mystery"], ["3", "Arnold", "rock", "Meredith", "science fiction"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-5x5-29</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="b">
+        <v>0</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Wrong plan</t>
+        </is>
+      </c>
+      <c r="E41" t="b">
+        <v>1</v>
+      </c>
+      <c r="F41" t="b">
+        <v>0</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Nationality", "Vacation", "Education", "Occupation"], "rows": [["1", "Alice", "german", "beach", "doctorate", "doctor"], ["2", "Arnold", "norwegian", "cruise", "associate", "lawyer"], ["3", "Bob", "dane", "city", "bachelor", "engineer"], ["4", "Eric", "brit", "camping", "master", "teacher"], ["5", "Peter", "swede", "mountain", "high school", "artist"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-6x4-9</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="b">
+        <v>0</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Wrong plan</t>
+        </is>
+      </c>
+      <c r="E42" t="b">
+        <v>1</v>
+      </c>
+      <c r="F42" t="b">
+        <v>0</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "PhoneModel",
+      "Nationality",
+      "Color"
+    ],
+    "rows": [
+      [
+        "1",
+        "Carol",
+        "xiaomi mi 11",
+        "chinese",
+        "green"
+      ],
+      [
+        "2",
+        "Arnold",
+        "oneplus 9",
+        "norwegian",
+        "purple"
+      ],
+      [
+        "3",
+        "Alice",
+        "google pixel 6",
+        "german",
+        "red"
+      ],
+      [
+        "4",
+        "Eric",
+        "huawei p50",
+        "dane",
+        "yellow"
+      ],
+      [
+        "5",
+        "Bob",
+        "samsung galaxy s21",
+        "swede",
+        "white"
+      ],
+      [
+        "6",
+        "Peter",
+        "iphone 13",
+        "brit",
+        "blue"
+      ]
+    ]
+  }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-3x5-19</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="b">
+        <v>0</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E43" t="b">
+        <v>1</v>
+      </c>
+      <c r="F43" t="b">
+        <v>1</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Occupation", "Education", "Smoothie", "Hobby"], "rows": [["1", "Arnold", "engineer", "high school", "watermelon", "gardening"], ["2", "Peter", "doctor", "associate", "desert", "cooking"], ["3", "Eric", "teacher", "bachelor", "cherry", "photography"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-4x5-32</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="b">
+        <v>0</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E44" t="b">
+        <v>1</v>
+      </c>
+      <c r="F44" t="b">
+        <v>1</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Hobby", "Birthday", "Education", "Smoothie"], "rows": [["1", "Arnold", "photography", "april", "associate", "dragonfruit"], ["2", "Eric", "gardening", "jan", "bachelor", "desert"], ["3", "Alice", "cooking", "sept", "high school", "cherry"], ["4", "Peter", "painting", "feb", "master", "watermelon"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-6x3-11</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="b">
+        <v>0</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Wrong plan</t>
+        </is>
+      </c>
+      <c r="E45" t="b">
+        <v>1</v>
+      </c>
+      <c r="F45" t="b">
+        <v>0</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "HairColor",
       "Height"
     ],
     "rows": [
@@ -3517,64 +3605,129 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E46" t="b">
+        <v>1</v>
+      </c>
+      <c r="F46" t="b">
+        <v>1</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Flower", "Hobby", "Pet", "Color", "HouseStyle"], "rows": [["1", "Peter", "daffodils", "gardening", "bird", "yellow", "ranch"], ["2", "Arnold", "carnations", "painting", "fish", "white", "craftsman"], ["3", "Alice", "roses", "photography", "dog", "red", "colonial"], ["4", "Eric", "lilies", "cooking", "cat", "green", "victorian"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-5x6-13</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="b">
+        <v>1</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E47" t="b">
+        <v>0</v>
+      </c>
+      <c r="F47" t="b">
+        <v>0</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 00:29:05.py", line 1
+    Checks all currently assigned houses (houses is a list of 5 elements; some may be None)
+           ^^^
+SyntaxError: invalid syntax</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-6x4-14</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="b">
+        <v>0</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
           <t>Wrong plan</t>
         </is>
       </c>
-      <c r="E46" t="b">
-        <v>0</v>
-      </c>
-      <c r="F46" t="b">
-        <v>0</v>
-      </c>
-      <c r="G46" t="inlineStr">
+      <c r="E48" t="b">
+        <v>1</v>
+      </c>
+      <c r="F48" t="b">
+        <v>0</v>
+      </c>
+      <c r="G48" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "Flower",
-      "Hobby",
-      "Pet",
-      "Color",
-      "House style"
+      "CarModel",
+      "Mother",
+      "Hobby"
     ],
     "rows": [
       [
         "1",
+        "Arnold",
+        "honda civic",
+        "Janelle",
+        "woodworking"
+      ],
+      [
+        "2",
+        "Eric",
+        "tesla model 3",
+        "Holly",
+        "gardening"
+      ],
+      [
+        "3",
         "Peter",
-        "daffodils",
-        "gardening",
-        "bird",
-        "yellow",
-        "ranch"
-      ],
-      [
-        "2",
-        "Arnold",
-        "carnations",
-        "painting",
-        "fish",
-        "white",
-        "craftsman"
-      ],
-      [
-        "3",
+        "chevrolet silverado",
+        "Aniya",
+        "knitting"
+      ],
+      [
+        "4",
+        "Carol",
+        "ford f150",
+        "Sarah",
+        "photography"
+      ],
+      [
+        "5",
+        "Bob",
+        "bmw 3 series",
+        "Penny",
+        "painting"
+      ],
+      [
+        "6",
         "Alice",
-        "roses",
-        "photography",
-        "dog",
-        "red",
-        "colonial"
-      ],
-      [
-        "4",
-        "Eric",
-        "lilies",
-        "cooking",
-        "cat",
-        "green",
-        "victorian"
+        "toyota camry",
+        "Kailyn",
+        "cooking"
       ]
     ]
   }
@@ -3582,70 +3735,6 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-5x6-13</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C47" t="b">
-        <v>1</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
-      <c r="E47" t="b">
-        <v>0</v>
-      </c>
-      <c r="F47" t="b">
-        <v>0</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-11 19:29:59.py", line 1
-    Return the current domain for attribute attr given available values and any pending constraint.
-           ^^^
-SyntaxError: invalid syntax</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-6x4-14</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>1</v>
-      </c>
-      <c r="C48" t="b">
-        <v>1</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
-      <c r="E48" t="b">
-        <v>0</v>
-      </c>
-      <c r="F48" t="b">
-        <v>0</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-11 19:29:59.py", line 1
-    Check the constraints that involve the houses in the current partial assignment.
-          ^^^
-SyntaxError: invalid syntax</t>
-        </is>
-      </c>
-    </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
@@ -3664,79 +3753,57 @@
         </is>
       </c>
       <c r="E49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="b">
         <v>1</v>
       </c>
       <c r="G49" t="inlineStr">
-        <is>
-          <t>{"solution": {"header": ["House", "Name", "occupation", "car"], "rows": [["1", "Eric", "doctor", "tesla model 3"], ["2", "Carol", "teacher", "bmw 3 series"], ["3", "Bob", "engineer", "honda civic"], ["4", "Peter", "nurse", "toyota camry"], ["5", "Arnold", "artist", "ford f150"], ["6", "Alice", "lawyer", "chevrolet silverado"]]}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-6x2-4</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C50" t="b">
-        <v>0</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Correct</t>
-        </is>
-      </c>
-      <c r="E50" t="b">
-        <v>0</v>
-      </c>
-      <c r="F50" t="b">
-        <v>1</v>
-      </c>
-      <c r="G50" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "phone"
+      "Occupation",
+      "CarModel"
     ],
     "rows": [
       [
         "1",
         "Eric",
-        "huawei p50"
+        "doctor",
+        "tesla model 3"
       ],
       [
         "2",
-        "Peter",
-        "samsung galaxy s21"
+        "Carol",
+        "teacher",
+        "bmw 3 series"
       ],
       [
         "3",
         "Bob",
-        "xiaomi mi 11"
+        "engineer",
+        "honda civic"
       ],
       [
         "4",
+        "Peter",
+        "nurse",
+        "toyota camry"
+      ],
+      [
+        "5",
+        "Arnold",
+        "artist",
+        "ford f150"
+      ],
+      [
+        "6",
         "Alice",
-        "iphone 13"
-      ],
-      [
-        "5",
-        "Carol",
-        "google pixel 6"
-      ],
-      [
-        "6",
-        "Arnold",
-        "oneplus 9"
+        "lawyer",
+        "chevrolet silverado"
       ]
     ]
   }
@@ -3744,6 +3811,35 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-6x2-4</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="b">
+        <v>0</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E50" t="b">
+        <v>1</v>
+      </c>
+      <c r="F50" t="b">
+        <v>1</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "PhoneModel"], "rows": [["1", "Eric", "huawei p50"], ["2", "Peter", "samsung galaxy s21"], ["3", "Bob", "xiaomi mi 11"], ["4", "Alice", "iphone 13"], ["5", "Carol", "google pixel 6"], ["6", "Arnold", "oneplus 9"]]}}</t>
+        </is>
+      </c>
+    </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
@@ -3758,16 +3854,103 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E51" t="b">
+        <v>1</v>
+      </c>
+      <c r="F51" t="b">
+        <v>1</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Height", "Cigar", "Smoothie", "PhoneModel"], "rows": [["1", "Peter", "short", "blends", "watermelon", "samsung galaxy s21"], ["2", "Eric", "very tall", "prince", "desert", "iphone 13"], ["3", "Arnold", "tall", "blue master", "cherry", "oneplus 9"], ["4", "Alice", "very short", "pall mall", "lime", "huawei p50"], ["5", "Bob", "average", "dunhill", "dragonfruit", "google pixel 6"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-2x4-14</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="b">
+        <v>0</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E52" t="b">
+        <v>1</v>
+      </c>
+      <c r="F52" t="b">
+        <v>1</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "HouseStyle", "Smoothie", "Pet"], "rows": [["1", "Arnold", "victorian", "cherry", "dog"], ["2", "Eric", "colonial", "desert", "cat"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-5x4-2</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="b">
+        <v>0</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E53" t="b">
+        <v>1</v>
+      </c>
+      <c r="F53" t="b">
+        <v>1</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Color", "PhoneModel", "Occupation"], "rows": [["1", "Eric", "green", "google pixel 6", "teacher"], ["2", "Bob", "blue", "samsung galaxy s21", "doctor"], ["3", "Peter", "red", "huawei p50", "artist"], ["4", "Alice", "yellow", "oneplus 9", "lawyer"], ["5", "Arnold", "white", "iphone 13", "engineer"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-5x4-26</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="b">
+        <v>0</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
           <t>Wrong plan</t>
         </is>
       </c>
-      <c r="E51" t="b">
-        <v>0</v>
-      </c>
-      <c r="F51" t="b">
-        <v>0</v>
-      </c>
-      <c r="G51" t="inlineStr">
+      <c r="E54" t="b">
+        <v>1</v>
+      </c>
+      <c r="F54" t="b">
+        <v>0</v>
+      </c>
+      <c r="G54" t="inlineStr">
         <is>
           <t>{
   "solution": {
@@ -3775,180 +3958,8 @@
       "House",
       "Name",
       "Height",
-      "cigar",
-      "smoothie",
-      "phone"
-    ],
-    "rows": []
-  }
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-2x4-14</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>1</v>
-      </c>
-      <c r="C52" t="b">
-        <v>0</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E52" t="b">
-        <v>0</v>
-      </c>
-      <c r="F52" t="b">
-        <v>0</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>{
-  "solution": {
-    "header": [
-      "House",
-      "Name",
-      "House Style",
-      "Smoothie",
-      "Pet"
-    ],
-    "rows": [
-      [
-        "1",
-        "Arnold",
-        "victorian",
-        "cherry",
-        "dog"
-      ],
-      [
-        "2",
-        "Eric",
-        "colonial",
-        "desert",
-        "cat"
-      ]
-    ]
-  }
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-5x4-2</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>1</v>
-      </c>
-      <c r="C53" t="b">
-        <v>0</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E53" t="b">
-        <v>0</v>
-      </c>
-      <c r="F53" t="b">
-        <v>0</v>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>{
-  "solution": {
-    "header": [
-      "House",
-      "Name",
-      "favorite color",
-      "phone models",
-      "occupation"
-    ],
-    "rows": [
-      [
-        "1",
-        "Eric",
-        "green",
-        "google pixel 6",
-        "teacher"
-      ],
-      [
-        "2",
-        "Bob",
-        "blue",
-        "samsung galaxy s21",
-        "doctor"
-      ],
-      [
-        "3",
-        "Peter",
-        "red",
-        "huawei p50",
-        "artist"
-      ],
-      [
-        "4",
-        "Alice",
-        "yellow",
-        "oneplus 9",
-        "lawyer"
-      ],
-      [
-        "5",
-        "Arnold",
-        "white",
-        "iphone 13",
-        "engineer"
-      ]
-    ]
-  }
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-5x4-26</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>1</v>
-      </c>
-      <c r="C54" t="b">
-        <v>0</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E54" t="b">
-        <v>0</v>
-      </c>
-      <c r="F54" t="b">
-        <v>0</v>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>{
-  "solution": {
-    "header": [
-      "House",
-      "Name",
-      "Height",
-      "Mother's name",
-      "Hair color"
+      "Mother",
+      "HairColor"
     ],
     "rows": [
       [
@@ -4010,287 +4021,165 @@
         </is>
       </c>
       <c r="E55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" t="b">
         <v>1</v>
       </c>
       <c r="G55" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "HouseStyle"], "rows": [["1", "Eric", "victorian"], ["2", "Arnold", "colonial"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-2x4-36</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="b">
+        <v>0</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E56" t="b">
+        <v>1</v>
+      </c>
+      <c r="F56" t="b">
+        <v>1</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "BookGenre", "Birthday", "Animal"], "rows": [["1", "Eric", "mystery", "sept", "horse"], ["2", "Arnold", "science fiction", "april", "cat"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-5x4-27</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="b">
+        <v>0</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E57" t="b">
+        <v>1</v>
+      </c>
+      <c r="F57" t="b">
+        <v>1</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Birthday", "Cigar", "Drink"], "rows": [["1", "Bob", "april", "prince", "milk"], ["2", "Alice", "feb", "blends", "tea"], ["3", "Eric", "jan", "pall mall", "root beer"], ["4", "Arnold", "sept", "blue master", "coffee"], ["5", "Peter", "mar", "dunhill", "water"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-3x3-29</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="b">
+        <v>0</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E58" t="b">
+        <v>1</v>
+      </c>
+      <c r="F58" t="b">
+        <v>1</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Mother", "Food"], "rows": [["1", "Eric", "Janelle", "grilled cheese"], ["2", "Arnold", "Aniya", "spaghetti"], ["3", "Peter", "Holly", "pizza"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-4x6-11</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="b">
+        <v>0</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E59" t="b">
+        <v>1</v>
+      </c>
+      <c r="F59" t="b">
+        <v>1</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Hobby", "Animal", "BookGenre", "Birthday", "MusicGenre"], "rows": [["1", "Peter", "painting", "fish", "fantasy", "feb", "pop"], ["2", "Alice", "cooking", "bird", "romance", "sept", "jazz"], ["3", "Arnold", "gardening", "horse", "mystery", "april", "rock"], ["4", "Eric", "photography", "cat", "science fiction", "jan", "classical"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-3x3-19</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="b">
+        <v>0</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E60" t="b">
+        <v>1</v>
+      </c>
+      <c r="F60" t="b">
+        <v>1</v>
+      </c>
+      <c r="G60" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "Style"
-    ],
-    "rows": [
-      [
-        "1",
-        "Eric",
-        "victorian"
-      ],
-      [
-        "2",
-        "Arnold",
-        "colonial"
-      ]
-    ]
-  }
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-2x4-36</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>1</v>
-      </c>
-      <c r="C56" t="b">
-        <v>0</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E56" t="b">
-        <v>0</v>
-      </c>
-      <c r="F56" t="b">
-        <v>0</v>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>{
-  "solution": {
-    "header": [
-      "House",
-      "Name",
-      "favorite book genres",
-      "birthday month",
-      "animals"
-    ],
-    "rows": [
-      [
-        "1",
-        "Eric",
-        "mystery",
-        "sept",
-        "horse"
-      ],
-      [
-        "2",
-        "Arnold",
-        "science fiction",
-        "april",
-        "cat"
-      ]
-    ]
-  }
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-5x4-27</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>1</v>
-      </c>
-      <c r="C57" t="b">
-        <v>0</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Correct</t>
-        </is>
-      </c>
-      <c r="E57" t="b">
-        <v>0</v>
-      </c>
-      <c r="F57" t="b">
-        <v>1</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>{
-  "solution": {
-    "header": [
-      "House",
-      "Name",
-      "birthday",
-      "cigar",
-      "drink"
-    ],
-    "rows": [
-      [
-        "1",
-        "Bob",
-        "april",
-        "prince",
-        "milk"
-      ],
-      [
-        "2",
-        "Alice",
-        "feb",
-        "blends",
-        "tea"
-      ],
-      [
-        "3",
-        "Eric",
-        "jan",
-        "pall mall",
-        "root beer"
-      ],
-      [
-        "4",
-        "Arnold",
-        "sept",
-        "blue master",
-        "coffee"
-      ],
-      [
-        "5",
-        "Peter",
-        "mar",
-        "dunhill",
-        "water"
-      ]
-    ]
-  }
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-3x3-29</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>1</v>
-      </c>
-      <c r="C58" t="b">
-        <v>0</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E58" t="b">
-        <v>0</v>
-      </c>
-      <c r="F58" t="b">
-        <v>0</v>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>{
-  "solution": {
-    "header": [
-      "House",
-      "Name",
-      "Mother",
-      "Lunch"
-    ],
-    "rows": [
-      [
-        "1",
-        "Eric",
-        "Janelle",
-        "grilled cheese"
-      ],
-      [
-        "2",
-        "Arnold",
-        "Aniya",
-        "spaghetti"
-      ],
-      [
-        "3",
-        "Peter",
-        "Holly",
-        "pizza"
-      ]
-    ]
-  }
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-4x6-11</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>1</v>
-      </c>
-      <c r="C59" t="b">
-        <v>0</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Correct</t>
-        </is>
-      </c>
-      <c r="E59" t="b">
-        <v>0</v>
-      </c>
-      <c r="F59" t="b">
-        <v>1</v>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>{"solution": {"header": ["House", "Name", "hobby", "animal", "book", "birthday", "music"], "rows": [["1", "Peter", "painting", "fish", "fantasy", "feb", "pop"], ["2", "Alice", "cooking", "bird", "romance", "sept", "jazz"], ["3", "Arnold", "gardening", "horse", "mystery", "april", "rock"], ["4", "Eric", "photography", "cat", "science fiction", "jan", "classical"]]}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-3x3-19</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>1</v>
-      </c>
-      <c r="C60" t="b">
-        <v>0</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E60" t="b">
-        <v>0</v>
-      </c>
-      <c r="F60" t="b">
-        <v>0</v>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>{
-  "solution": {
-    "header": [
-      "House",
-      "Name",
-      "favorite smoothie",
-      "favorite book genre"
+      "Smoothie",
+      "BookGenre"
     ],
     "rows": [
       [
@@ -4331,14 +4220,14 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Wrong plan</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -4348,7 +4237,7 @@
       "House",
       "Name",
       "Height",
-      "Lunch"
+      "Food"
     ],
     "rows": [
       [
@@ -4405,50 +4294,84 @@
         </is>
       </c>
       <c r="E62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" t="b">
         <v>1</v>
       </c>
       <c r="G62" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Cigar"], "rows": [["1", "Peter", "dunhill"], ["2", "Arnold", "yellow monster"], ["3", "Bob", "pall mall"], ["4", "Alice", "blends"], ["5", "Carol", "blue master"], ["6", "Eric", "prince"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-4x5-14</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" t="b">
+        <v>0</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Wrong plan</t>
+        </is>
+      </c>
+      <c r="E63" t="b">
+        <v>1</v>
+      </c>
+      <c r="F63" t="b">
+        <v>0</v>
+      </c>
+      <c r="G63" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "favorite cigar"
+      "Mother",
+      "Smoothie",
+      "Height",
+      "Education"
     ],
     "rows": [
       [
         "1",
+        "Eric",
+        "Kailyn",
+        "watermelon",
+        "very short",
+        "associate"
+      ],
+      [
+        "2",
         "Peter",
-        "dunhill"
-      ],
-      [
-        "2",
+        "Aniya",
+        "cherry",
+        "average",
+        "high school"
+      ],
+      [
+        "3",
+        "Alice",
+        "Janelle",
+        "dragonfruit",
+        "tall",
+        "bachelor"
+      ],
+      [
+        "4",
         "Arnold",
-        "yellow monster"
-      ],
-      [
-        "3",
-        "Bob",
-        "pall mall"
-      ],
-      [
-        "4",
-        "Alice",
-        "blends"
-      ],
-      [
-        "5",
-        "Carol",
-        "blue master"
-      ],
-      [
-        "6",
-        "Eric",
-        "prince"
+        "Holly",
+        "desert",
+        "short",
+        "master"
       ]
     ]
   }
@@ -4456,35 +4379,6 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-4x5-14</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>1</v>
-      </c>
-      <c r="C63" t="b">
-        <v>0</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Correct</t>
-        </is>
-      </c>
-      <c r="E63" t="b">
-        <v>0</v>
-      </c>
-      <c r="F63" t="b">
-        <v>1</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>{"solution": {"header": ["House", "Name", "Mother", "Favorite Smoothie", "Height", "Education"], "rows": [["1", "Eric", "Kailyn", "watermelon", "very short", "associate"], ["2", "Peter", "Aniya", "cherry", "average", "high school"], ["3", "Alice", "Janelle", "dragonfruit", "tall", "bachelor"], ["4", "Arnold", "Holly", "desert", "short", "master"]]}}</t>
-        </is>
-      </c>
-    </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
@@ -4503,14 +4397,14 @@
         </is>
       </c>
       <c r="E64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="b">
         <v>1</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>{"solution": {"header": ["House", "Name", "Child"], "rows": [["1", "Bob", "Timothy"], ["2", "Alice", "Fred"], ["3", "Arnold", "Bella"], ["4", "Eric", "Samantha"], ["5", "Peter", "Meredith"]]}}</t>
+          <t>{"solution": {"header": ["House", "Name", "Children"], "rows": [["1", "Bob", "Timothy"], ["2", "Alice", "Fred"], ["3", "Arnold", "Bella"], ["4", "Eric", "Samantha"], ["5", "Peter", "Meredith"]]}}</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4433,48 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>{"solution": {"header": ["House", "Name", "Smoothie", "Nationality"], "rows": [["1", "Arnold", "lime", "swede"], ["2", "Peter", "dragonfruit", "german"], ["3", "Alice", "watermelon", "norwegian"], ["4", "Bob", "desert", "dane"], ["5", "Eric", "cherry", "brit"]]}}</t>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "Smoothie",
+      "Nationality"
+    ],
+    "rows": [
+      [
+        "1",
+        "Arnold",
+        "lime",
+        "swede"
+      ],
+      [
+        "2",
+        "Peter",
+        "dragonfruit",
+        "german"
+      ],
+      [
+        "3",
+        "Alice",
+        "watermelon",
+        "norwegian"
+      ],
+      [
+        "4",
+        "Bob",
+        "desert",
+        "dane"
+      ],
+      [
+        "5",
+        "Eric",
+        "cherry",
+        "brit"
+      ]
+    ]
+  }
+}</t>
         </is>
       </c>
     </row>
@@ -4561,14 +4496,14 @@
         </is>
       </c>
       <c r="E66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" t="b">
         <v>1</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>{"solution": {"header": ["House", "Name", "Style"], "rows": [["1", "Peter", "ranch"], ["2", "Alice", "victorian"], ["3", "Eric", "craftsman"], ["4", "Arnold", "colonial"]]}}</t>
+          <t>{"solution": {"header": ["House", "Name", "HouseStyle"], "rows": [["1", "Peter", "ranch"], ["2", "Alice", "victorian"], ["3", "Eric", "craftsman"], ["4", "Arnold", "colonial"]]}}</t>
         </is>
       </c>
     </row>
@@ -4590,7 +4525,7 @@
         </is>
       </c>
       <c r="E67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67" t="b">
         <v>0</v>
@@ -4603,9 +4538,9 @@
       "House",
       "Name",
       "Birthday",
-      "Lunch",
+      "Food",
       "Height",
-      "Car Model"
+      "CarModel"
     ],
     "rows": [
       [
@@ -4680,50 +4615,105 @@
         </is>
       </c>
       <c r="E68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" t="b">
         <v>1</v>
       </c>
       <c r="G68" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Vacation"], "rows": [["1", "Alice", "mountain"], ["2", "Eric", "camping"], ["3", "Peter", "cultural"], ["4", "Carol", "city"], ["5", "Bob", "cruise"], ["6", "Arnold", "beach"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-6x3-18</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" t="b">
+        <v>0</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E69" t="b">
+        <v>1</v>
+      </c>
+      <c r="F69" t="b">
+        <v>1</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Mother", "Pet"], "rows": [["1", "Bob", "Penny", "dog"], ["2", "Peter", "Sarah", "fish"], ["3", "Arnold", "Janelle", "cat"], ["4", "Alice", "Holly", "bird"], ["5", "Carol", "Aniya", "hamster"], ["6", "Eric", "Kailyn", "rabbit"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-3x5-17</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" t="b">
+        <v>0</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E70" t="b">
+        <v>1</v>
+      </c>
+      <c r="F70" t="b">
+        <v>1</v>
+      </c>
+      <c r="G70" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "vacation"
+      "PhoneModel",
+      "Height",
+      "HouseStyle",
+      "CarModel"
     ],
     "rows": [
       [
         "1",
-        "Alice",
-        "mountain"
+        "Eric",
+        "iphone 13",
+        "average",
+        "ranch",
+        "toyota camry"
       ],
       [
         "2",
-        "Eric",
-        "camping"
+        "Arnold",
+        "google pixel 6",
+        "short",
+        "colonial",
+        "ford f150"
       ],
       [
         "3",
         "Peter",
-        "cultural"
-      ],
-      [
-        "4",
-        "Carol",
-        "city"
-      ],
-      [
-        "5",
-        "Bob",
-        "cruise"
-      ],
-      [
-        "6",
-        "Arnold",
-        "beach"
+        "samsung galaxy s21",
+        "very short",
+        "victorian",
+        "tesla model 3"
       ]
     ]
   }
@@ -4731,111 +4721,6 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-6x3-18</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>1</v>
-      </c>
-      <c r="C69" t="b">
-        <v>0</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Correct</t>
-        </is>
-      </c>
-      <c r="E69" t="b">
-        <v>0</v>
-      </c>
-      <c r="F69" t="b">
-        <v>1</v>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>{
-  "solution": {
-    "header": [
-      "House",
-      "Name",
-      "mother",
-      "pet"
-    ],
-    "rows": [
-      [
-        "1",
-        "Bob",
-        "Penny",
-        "dog"
-      ],
-      [
-        "2",
-        "Peter",
-        "Sarah",
-        "fish"
-      ],
-      [
-        "3",
-        "Arnold",
-        "Janelle",
-        "cat"
-      ],
-      [
-        "4",
-        "Alice",
-        "Holly",
-        "bird"
-      ],
-      [
-        "5",
-        "Carol",
-        "Aniya",
-        "hamster"
-      ],
-      [
-        "6",
-        "Eric",
-        "Kailyn",
-        "rabbit"
-      ]
-    ]
-  }
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-3x5-17</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>1</v>
-      </c>
-      <c r="C70" t="b">
-        <v>0</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E70" t="b">
-        <v>0</v>
-      </c>
-      <c r="F70" t="b">
-        <v>0</v>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>{"solution": {"header": ["House", "Name", "phone", "height", "style", "car"], "rows": [["1", "Eric", "iphone 13", "average", "ranch", "toyota camry"], ["2", "Arnold", "google pixel 6", "short", "colonial", "ford f150"], ["3", "Peter", "samsung galaxy s21", "very short", "victorian", "tesla model 3"]]}}</t>
-        </is>
-      </c>
-    </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
@@ -4850,41 +4735,18 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Wrong plan</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>{
-  "solution": {
-    "header": [
-      "House",
-      "Name",
-      "child",
-      "lunch"
-    ],
-    "rows": [
-      [
-        "1",
-        "Eric",
-        "Bella",
-        "grilled cheese"
-      ],
-      [
-        "2",
-        "Arnold",
-        "Fred",
-        "pizza"
-      ]
-    ]
-  }
-}</t>
+          <t>{"solution": {"header": ["House", "Name", "Children", "Food"], "rows": [["1", "Eric", "Bella", "grilled cheese"], ["2", "Arnold", "Fred", "pizza"]]}}</t>
         </is>
       </c>
     </row>
@@ -4964,14 +4826,14 @@
         </is>
       </c>
       <c r="E73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="b">
         <v>1</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>{"solution": {"header": ["House", "Name", "birthday month", "mother's name"], "rows": [["1", "Eric", "april", "Aniya"], ["2", "Arnold", "sept", "Holly"]]}}</t>
+          <t>{"solution": {"header": ["House", "Name", "Birthday", "Mother"], "rows": [["1", "Eric", "april", "Aniya"], ["2", "Arnold", "sept", "Holly"]]}}</t>
         </is>
       </c>
     </row>
@@ -4999,34 +4861,97 @@
         <v>1</v>
       </c>
       <c r="G74" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Occupation"], "rows": [["1", "Eric", "doctor"], ["2", "Arnold", "engineer"], ["3", "Alice", "artist"], ["4", "Peter", "teacher"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-4x5-25</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" t="b">
+        <v>0</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E75" t="b">
+        <v>1</v>
+      </c>
+      <c r="F75" t="b">
+        <v>1</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "HouseStyle", "HairColor", "Children", "BookGenre"], "rows": [["1", "Arnold", "victorian", "red", "Meredith", "science fiction"], ["2", "Eric", "ranch", "black", "Fred", "mystery"], ["3", "Peter", "craftsman", "blonde", "Bella", "fantasy"], ["4", "Alice", "colonial", "brown", "Samantha", "romance"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-4x3-38</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>1</v>
+      </c>
+      <c r="C76" t="b">
+        <v>0</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E76" t="b">
+        <v>1</v>
+      </c>
+      <c r="F76" t="b">
+        <v>1</v>
+      </c>
+      <c r="G76" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "Occupation"
+      "Mother",
+      "Flower"
     ],
     "rows": [
       [
         "1",
         "Eric",
-        "doctor"
+        "Aniya",
+        "daffodils"
       ],
       [
         "2",
         "Arnold",
-        "engineer"
+        "Holly",
+        "lilies"
       ],
       [
         "3",
         "Alice",
-        "artist"
+        "Kailyn",
+        "carnations"
       ],
       [
         "4",
         "Peter",
-        "teacher"
+        "Janelle",
+        "roses"
       ]
     ]
   }
@@ -5034,73 +4959,83 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-4x5-25</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>1</v>
-      </c>
-      <c r="C75" t="b">
-        <v>0</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E75" t="b">
-        <v>0</v>
-      </c>
-      <c r="F75" t="b">
-        <v>0</v>
-      </c>
-      <c r="G75" t="inlineStr">
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-2x3-31</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>1</v>
+      </c>
+      <c r="C77" t="b">
+        <v>0</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E77" t="b">
+        <v>1</v>
+      </c>
+      <c r="F77" t="b">
+        <v>1</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "FavoriteSport", "Hobby"], "rows": [["1", "Arnold", "basketball", "gardening"], ["2", "Eric", "soccer", "photography"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-2x4-23</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>1</v>
+      </c>
+      <c r="C78" t="b">
+        <v>0</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E78" t="b">
+        <v>1</v>
+      </c>
+      <c r="F78" t="b">
+        <v>1</v>
+      </c>
+      <c r="G78" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "Style",
-      "Hair",
-      "Child",
-      "Favorite Book Genre"
+      "Mother",
+      "CarModel",
+      "Height"
     ],
     "rows": [
       [
         "1",
         "Arnold",
-        "victorian",
-        "red",
-        "Meredith",
-        "science fiction"
+        "Aniya",
+        "ford f150",
+        "short"
       ],
       [
         "2",
         "Eric",
-        "ranch",
-        "black",
-        "Fred",
-        "mystery"
-      ],
-      [
-        "3",
-        "Peter",
-        "craftsman",
-        "blonde",
-        "Bella",
-        "fantasy"
-      ],
-      [
-        "4",
-        "Alice",
-        "colonial",
-        "brown",
-        "Samantha",
-        "romance"
+        "Holly",
+        "tesla model 3",
+        "very short"
       ]
     ]
   }
@@ -5108,308 +5043,125 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-4x3-38</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>1</v>
-      </c>
-      <c r="C76" t="b">
-        <v>0</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Correct</t>
-        </is>
-      </c>
-      <c r="E76" t="b">
-        <v>0</v>
-      </c>
-      <c r="F76" t="b">
-        <v>1</v>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>{"solution": {"header": ["House", "Name", "Mother's Name", "Favorite Flower"], "rows": [["1", "Eric", "Aniya", "daffodils"], ["2", "Arnold", "Holly", "lilies"], ["3", "Alice", "Kailyn", "carnations"], ["4", "Peter", "Janelle", "roses"]]}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-2x3-31</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>1</v>
-      </c>
-      <c r="C77" t="b">
-        <v>0</v>
-      </c>
-      <c r="D77" t="inlineStr">
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-5x4-31</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" t="b">
+        <v>0</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E79" t="b">
+        <v>1</v>
+      </c>
+      <c r="F79" t="b">
+        <v>1</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Vacation", "Children", "Nationality"], "rows": [["1", "Peter", "cruise", "Fred", "norwegian"], ["2", "Bob", "camping", "Timothy", "german"], ["3", "Eric", "city", "Bella", "swede"], ["4", "Alice", "beach", "Meredith", "brit"], ["5", "Arnold", "mountain", "Samantha", "dane"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-3x5-0</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>1</v>
+      </c>
+      <c r="C80" t="b">
+        <v>0</v>
+      </c>
+      <c r="D80" t="inlineStr">
         <is>
           <t>Wrong plan</t>
         </is>
       </c>
-      <c r="E77" t="b">
-        <v>0</v>
-      </c>
-      <c r="F77" t="b">
-        <v>0</v>
-      </c>
-      <c r="G77" t="inlineStr">
+      <c r="E80" t="b">
+        <v>0</v>
+      </c>
+      <c r="F80" t="b">
+        <v>0</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "BookGenre", "Smoothie", "Birthday", "Height"], "rows": [["1", "Eric", "romance", "watermelon", "april", "very short"], ["2", "Peter", "science fiction", "desert", "jan", "average"], ["3", "Arnold", "mystery", "cherry", "sept", "short"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-2x4-4</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" t="b">
+        <v>0</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E81" t="b">
+        <v>1</v>
+      </c>
+      <c r="F81" t="b">
+        <v>1</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "HouseStyle", "Height", "Education"], "rows": [["1", "Arnold", "victorian", "short", "associate"], ["2", "Eric", "colonial", "very short", "high school"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-2x3-3</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" t="b">
+        <v>0</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E82" t="b">
+        <v>1</v>
+      </c>
+      <c r="F82" t="b">
+        <v>1</v>
+      </c>
+      <c r="G82" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "favorite sports",
-      "hobby"
-    ],
-    "rows": [
-      [
-        "1",
-        "Arnold",
-        "basketball",
-        "gardening"
-      ],
-      [
-        "2",
-        "Eric",
-        "soccer",
-        "photography"
-      ]
-    ]
-  }
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-2x4-23</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>1</v>
-      </c>
-      <c r="C78" t="b">
-        <v>0</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E78" t="b">
-        <v>0</v>
-      </c>
-      <c r="F78" t="b">
-        <v>0</v>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>{"solution": {"header": ["House", "Name", "mothers' names", "car models", "heights"], "rows": [["1", "Arnold", "Aniya", "ford f150", "short"], ["2", "Eric", "Holly", "tesla model 3", "very short"]]}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-5x4-31</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>1</v>
-      </c>
-      <c r="C79" t="b">
-        <v>0</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Correct</t>
-        </is>
-      </c>
-      <c r="E79" t="b">
-        <v>0</v>
-      </c>
-      <c r="F79" t="b">
-        <v>1</v>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>{
-  "solution": {
-    "header": [
-      "House",
-      "Name",
-      "vacation",
-      "child",
-      "nationality"
-    ],
-    "rows": [
-      [
-        "1",
-        "Peter",
-        "cruise",
-        "Fred",
-        "norwegian"
-      ],
-      [
-        "2",
-        "Bob",
-        "camping",
-        "Timothy",
-        "german"
-      ],
-      [
-        "3",
-        "Eric",
-        "city",
-        "Bella",
-        "swede"
-      ],
-      [
-        "4",
-        "Alice",
-        "beach",
-        "Meredith",
-        "brit"
-      ],
-      [
-        "5",
-        "Arnold",
-        "mountain",
-        "Samantha",
-        "dane"
-      ]
-    ]
-  }
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-3x5-0</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>1</v>
-      </c>
-      <c r="C80" t="b">
-        <v>0</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E80" t="b">
-        <v>0</v>
-      </c>
-      <c r="F80" t="b">
-        <v>0</v>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>{"solution": {"header": ["House", "Name", "favorite book genre", "favorite smoothie", "birthday month", "height"], "rows": [["1", "Eric", "science fiction", "watermelon", "april", "short"], ["2", "Arnold", "mystery", "desert", "sept", "average"], ["3", "Peter", "romance", "cherry", "jan", "very short"]]}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-2x4-4</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>1</v>
-      </c>
-      <c r="C81" t="b">
-        <v>0</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E81" t="b">
-        <v>0</v>
-      </c>
-      <c r="F81" t="b">
-        <v>0</v>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>{
-  "solution": {
-    "header": [
-      "House",
-      "Name",
-      "style",
-      "height",
-      "level of education"
-    ],
-    "rows": [
-      [
-        "1",
-        "Arnold",
-        "victorian",
-        "short",
-        "associate"
-      ],
-      [
-        "2",
-        "Eric",
-        "colonial",
-        "very short",
-        "high school"
-      ]
-    ]
-  }
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-2x3-3</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>1</v>
-      </c>
-      <c r="C82" t="b">
-        <v>0</v>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E82" t="b">
-        <v>0</v>
-      </c>
-      <c r="F82" t="b">
-        <v>0</v>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>{
-  "solution": {
-    "header": [
-      "House",
-      "Name",
-      "lunch",
-      "mothers' names"
+      "Food",
+      "Mother"
     ],
     "rows": [
       [
@@ -5448,14 +5200,14 @@
         </is>
       </c>
       <c r="E83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" t="b">
         <v>1</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>{"solution": {"header": ["House", "Name", "Cigar", "Animal", "Child", "Book", "Phone"], "rows": [["1", "Peter", "blue master", "bird", "Fred", "mystery", "google pixel 6"], ["2", "Arnold", "pall mall", "horse", "Meredith", "romance", "iphone 13"], ["3", "Eric", "prince", "cat", "Bella", "science fiction", "samsung galaxy s21"]]}}</t>
+          <t>{"solution": {"header": ["House", "Name", "Cigar", "Animal", "Children", "BookGenre", "PhoneModel"], "rows": [["1", "Peter", "blue master", "bird", "Fred", "mystery", "google pixel 6"], ["2", "Arnold", "pall mall", "horse", "Meredith", "romance", "iphone 13"], ["3", "Eric", "prince", "cat", "Bella", "science fiction", "samsung galaxy s21"]]}}</t>
         </is>
       </c>
     </row>
@@ -5477,125 +5229,77 @@
         </is>
       </c>
       <c r="E84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" t="b">
         <v>1</v>
       </c>
       <c r="G84" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Smoothie", "FavoriteSport", "CarModel", "Flower"], "rows": [["1", "Eric", "cherry", "tennis", "tesla model 3", "roses"], ["2", "Alice", "desert", "soccer", "toyota camry", "carnations"], ["3", "Arnold", "watermelon", "basketball", "ford f150", "lilies"], ["4", "Peter", "dragonfruit", "swimming", "honda civic", "daffodils"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-6x6-29</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" t="b">
+        <v>0</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Wrong plan</t>
+        </is>
+      </c>
+      <c r="E85" t="b">
+        <v>1</v>
+      </c>
+      <c r="F85" t="b">
+        <v>0</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "HouseStyle", "Food", "Vacation", "Height", "Cigar"], "rows": [["1", "Carol", "colonial", "stir fry", "city", "average", "pall mall"], ["2", "Bob", "craftsman", "pizza", "cultural", "very short", "prince"], ["3", "Peter", "modern", "grilled cheese", "camping", "short", "blends"], ["4", "Eric", "ranch", "soup", "beach", "tall", "blue master"], ["5", "Alice", "victorian", "spaghetti", "mountain", "very tall", "yellow monster"], ["6", "Arnold", "mediterranean", "stew", "cruise", "super tall", "dunhill"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-2x2-32</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" t="b">
+        <v>0</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E86" t="b">
+        <v>1</v>
+      </c>
+      <c r="F86" t="b">
+        <v>1</v>
+      </c>
+      <c r="G86" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "Smoothie",
-      "Sport",
-      "Car",
-      "Flower"
-    ],
-    "rows": [
-      [
-        "1",
-        "Eric",
-        "cherry",
-        "tennis",
-        "tesla model 3",
-        "roses"
-      ],
-      [
-        "2",
-        "Alice",
-        "desert",
-        "soccer",
-        "toyota camry",
-        "carnations"
-      ],
-      [
-        "3",
-        "Arnold",
-        "watermelon",
-        "basketball",
-        "ford f150",
-        "lilies"
-      ],
-      [
-        "4",
-        "Peter",
-        "dragonfruit",
-        "swimming",
-        "honda civic",
-        "daffodils"
-      ]
-    ]
-  }
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-6x6-29</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>1</v>
-      </c>
-      <c r="C85" t="b">
-        <v>1</v>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
-      <c r="E85" t="b">
-        <v>0</v>
-      </c>
-      <c r="F85" t="b">
-        <v>0</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-11 19:29:59.py", line 1
-    This program solves the 6‐house logic puzzle by searching for an assignment
-                             ^
-SyntaxError: invalid character '‐' (U+2010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-2x2-32</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>1</v>
-      </c>
-      <c r="C86" t="b">
-        <v>0</v>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E86" t="b">
-        <v>0</v>
-      </c>
-      <c r="F86" t="b">
-        <v>0</v>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>{
-  "solution": {
-    "header": [
-      "House",
-      "Name",
-      "favorite book genres"
+      "BookGenre"
     ],
     "rows": [
       [
@@ -5628,14 +5332,14 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Correct</t>
+          <t>Wrong plan</t>
         </is>
       </c>
       <c r="E87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -5663,7 +5367,7 @@
         "Arnold",
         "tea",
         "white",
-        "roses",
+        "daffodils",
         "photography"
       ],
       [
@@ -5671,7 +5375,7 @@
         "Peter",
         "water",
         "red",
-        "daffodils",
+        "roses",
         "knitting"
       ],
       [
@@ -5710,47 +5414,18 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Wrong plan</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>{
-  "solution": {
-    "header": [
-      "House",
-      "Name",
-      "Book Genre",
-      "Vacation",
-      "Animal",
-      "Music Genre"
-    ],
-    "rows": [
-      [
-        "1",
-        "Arnold",
-        "mystery",
-        "mountain",
-        "cat",
-        "rock"
-      ],
-      [
-        "2",
-        "Eric",
-        "science fiction",
-        "beach",
-        "horse",
-        "pop"
-      ]
-    ]
-  }
-}</t>
+          <t>{"solution": {"header": ["House", "Name", "BookGenre", "Vacation", "Animal", "MusicGenre"], "rows": [["1", "Arnold", "mystery", "mountain", "cat", "rock"], ["2", "Eric", "science fiction", "beach", "horse", "pop"]]}}</t>
         </is>
       </c>
     </row>
@@ -5779,10 +5454,10 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-11 19:29:59.py", line 1
-    This program uses backtracking to solve the 6‐house Zebra logic puzzle.
-                                                 ^
-SyntaxError: invalid character '‐' (U+2010)</t>
+          <t>File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 00:29:05.py", line 1
+    This program uses a recursive backtracking algorithm to solve the Zebra puzzle.
+         ^^^^^^^
+SyntaxError: invalid syntax</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5479,7 @@
         </is>
       </c>
       <c r="E90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F90" t="b">
         <v>1</v>
@@ -5817,7 +5492,7 @@
       "House",
       "Name",
       "Height",
-      "Phone"
+      "PhoneModel"
     ],
     "rows": [
       [
@@ -5876,14 +5551,14 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Wrong plan</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -5892,9 +5567,9 @@
     "header": [
       "House",
       "Name",
-      "favorite cigar",
-      "favorite sport",
-      "favorite drink"
+      "Cigar",
+      "FavoriteSport",
+      "Drink"
     ],
     "rows": [
       [
@@ -5945,91 +5620,56 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Wrong plan</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G92" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "HairColor", "FavoriteSport"], "rows": [["1", "Arnold", "brown", "basketball"], ["2", "Alice", "red", "swimming"], ["3", "Peter", "black", "tennis"], ["4", "Eric", "blonde", "soccer"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-5x6-37</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" t="b">
+        <v>0</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E93" t="b">
+        <v>1</v>
+      </c>
+      <c r="F93" t="b">
+        <v>1</v>
+      </c>
+      <c r="G93" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "hair color",
-      "favorite sport"
-    ],
-    "rows": [
-      [
-        "1",
-        "Arnold",
-        "brown",
-        "basketball"
-      ],
-      [
-        "2",
-        "Alice",
-        "red",
-        "swimming"
-      ],
-      [
-        "3",
-        "Peter",
-        "black",
-        "tennis"
-      ],
-      [
-        "4",
-        "Eric",
-        "blonde",
-        "soccer"
-      ]
-    ]
-  }
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-5x6-37</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>1</v>
-      </c>
-      <c r="C93" t="b">
-        <v>0</v>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E93" t="b">
-        <v>0</v>
-      </c>
-      <c r="F93" t="b">
-        <v>0</v>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>{
-  "solution": {
-    "header": [
-      "House",
-      "Name",
-      "hobby",
-      "favorite sport",
-      "house style",
-      "child",
-      "height"
+      "Hobby",
+      "FavoriteSport",
+      "HouseStyle",
+      "Children",
+      "Height"
     ],
     "rows": [
       [
@@ -6093,11 +5733,11 @@
         <v>1</v>
       </c>
       <c r="C94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Wrong plan</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="E94" t="b">
@@ -6108,139 +5748,59 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>{"solution": {"header": ["House", "Name", "lunch"], "rows": [["1", "Eric", "grilled cheese"], ["2", "Arnold", "pizza"]]}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-2x3-32</t>
-        </is>
-      </c>
-      <c r="B95" t="n">
-        <v>1</v>
-      </c>
-      <c r="C95" t="b">
-        <v>1</v>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
-      <c r="E95" t="b">
-        <v>0</v>
-      </c>
-      <c r="F95" t="b">
-        <v>0</v>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
           <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-11 19:29:59.py", line 2, in &lt;module&gt;
+  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 00:29:05.py", line 2, in &lt;module&gt;
     main()
     ^^^^
 NameError: name 'main' is not defined. Did you mean: 'min'?</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-2x2-25</t>
-        </is>
-      </c>
-      <c r="B96" t="n">
-        <v>1</v>
-      </c>
-      <c r="C96" t="b">
-        <v>0</v>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Correct</t>
-        </is>
-      </c>
-      <c r="E96" t="b">
-        <v>0</v>
-      </c>
-      <c r="F96" t="b">
-        <v>1</v>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>{"solution": {"header": ["House", "Name", "vacation"], "rows": [["1", "Eric", "beach"], ["2", "Arnold", "mountain"]]}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-4x5-6</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
-        <v>1</v>
-      </c>
-      <c r="C97" t="b">
-        <v>0</v>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E97" t="b">
-        <v>0</v>
-      </c>
-      <c r="F97" t="b">
-        <v>0</v>
-      </c>
-      <c r="G97" t="inlineStr">
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-2x3-32</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" t="b">
+        <v>0</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E95" t="b">
+        <v>1</v>
+      </c>
+      <c r="F95" t="b">
+        <v>1</v>
+      </c>
+      <c r="G95" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "Education",
-      "Favorite music",
-      "Favorite color",
-      "Favorite flower"
+      "Birthday",
+      "Color"
     ],
     "rows": [
       [
         "1",
         "Arnold",
-        "bachelor",
-        "jazz",
-        "yellow",
-        "daffodils"
+        "april",
+        "red"
       ],
       [
         "2",
-        "Peter",
-        "associate",
-        "pop",
-        "green",
-        "roses"
-      ],
-      [
-        "3",
-        "Alice",
-        "master",
-        "rock",
-        "red",
-        "carnations"
-      ],
-      [
-        "4",
         "Eric",
-        "high school",
-        "classical",
-        "white",
-        "lilies"
+        "sept",
+        "yellow"
       ]
     ]
   }
@@ -6248,6 +5808,64 @@
         </is>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-2x2-25</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E96" t="b">
+        <v>1</v>
+      </c>
+      <c r="F96" t="b">
+        <v>1</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Vacation"], "rows": [["1", "Eric", "beach"], ["2", "Arnold", "mountain"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-4x5-6</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" t="b">
+        <v>0</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Wrong plan</t>
+        </is>
+      </c>
+      <c r="E97" t="b">
+        <v>0</v>
+      </c>
+      <c r="F97" t="b">
+        <v>0</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Education", "MusicGenre", "Color", "Flower"], "rows": [["1", "Peter", "high school", "rock", "red", "lilies"], ["2", "Alice", "master", "pop", "white", "carnations"], ["3", "Eric", "associate", "classical", "green", "roses"], ["4", "Arnold", "bachelor", "jazz", "yellow", "daffodils"]]}}</t>
+        </is>
+      </c>
+    </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
@@ -6266,47 +5884,71 @@
         </is>
       </c>
       <c r="E98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98" t="b">
         <v>1</v>
       </c>
       <c r="G98" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Cigar", "Hobby", "Education", "Drink"], "rows": [["1", "Peter", "pall mall", "gardening", "bachelor", "water"], ["2", "Arnold", "blue master", "photography", "associate", "milk"], ["3", "Eric", "prince", "cooking", "high school", "tea"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-2x6-1</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" t="b">
+        <v>0</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E99" t="b">
+        <v>1</v>
+      </c>
+      <c r="F99" t="b">
+        <v>1</v>
+      </c>
+      <c r="G99" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "favorite cigar",
-      "hobby",
-      "level of education",
-      "favorite drink"
+      "FavoriteSport",
+      "HairColor",
+      "Height",
+      "Smoothie",
+      "Flower"
     ],
     "rows": [
       [
         "1",
-        "Peter",
-        "pall mall",
-        "gardening",
-        "bachelor",
-        "water"
+        "Eric",
+        "soccer",
+        "black",
+        "short",
+        "desert",
+        "carnations"
       ],
       [
         "2",
         "Arnold",
-        "blue master",
-        "photography",
-        "associate",
-        "milk"
-      ],
-      [
-        "3",
-        "Eric",
-        "prince",
-        "cooking",
-        "high school",
-        "tea"
+        "basketball",
+        "brown",
+        "very short",
+        "cherry",
+        "daffodils"
       ]
     ]
   }
@@ -6314,35 +5956,6 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-2x6-1</t>
-        </is>
-      </c>
-      <c r="B99" t="n">
-        <v>1</v>
-      </c>
-      <c r="C99" t="b">
-        <v>0</v>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E99" t="b">
-        <v>0</v>
-      </c>
-      <c r="F99" t="b">
-        <v>0</v>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>{"solution": {"header": ["House", "Name", "favorite sports", "hair colors", "heights", "favorite smoothie", "favorite flower"], "rows": [["1", "Eric", "soccer", "black", "short", "desert", "carnations"], ["2", "Arnold", "basketball", "brown", "very short", "cherry", "daffodils"]]}}</t>
-        </is>
-      </c>
-    </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
@@ -6361,14 +5974,14 @@
         </is>
       </c>
       <c r="E100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F100" t="b">
         <v>1</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>{"solution": {"header": ["House", "Name", "car", "birthday", "hobby"], "rows": [["1", "Alice", "honda civic", "sept", "photography"], ["2", "Arnold", "tesla model 3", "april", "painting"], ["3", "Eric", "ford f150", "feb", "cooking"], ["4", "Peter", "toyota camry", "jan", "gardening"]]}}</t>
+          <t>{"solution": {"header": ["House", "Name", "CarModel", "Birthday", "Hobby"], "rows": [["1", "Alice", "honda civic", "sept", "photography"], ["2", "Arnold", "tesla model 3", "april", "painting"], ["3", "Eric", "ford f150", "feb", "cooking"], ["4", "Peter", "toyota camry", "jan", "gardening"]]}}</t>
         </is>
       </c>
     </row>
@@ -6390,7 +6003,7 @@
         </is>
       </c>
       <c r="E101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101" t="b">
         <v>0</v>
@@ -6402,45 +6015,45 @@
     "header": [
       "House",
       "Name",
-      "smoothie",
-      "animal",
-      "nationality"
+      "Smoothie",
+      "Animal",
+      "Nationality"
     ],
     "rows": [
       [
         "1",
-        "Alice",
-        "lime",
-        "fish",
-        "norwegian"
-      ],
-      [
-        "2",
         "Eric",
         "cherry",
         "cat",
-        "brit"
+        "swede"
+      ],
+      [
+        "2",
+        "Peter",
+        "desert",
+        "dog",
+        "german"
       ],
       [
         "3",
-        "Peter",
-        "dragonfruit",
+        "Arnold",
+        "lime",
         "horse",
         "dane"
       ],
       [
         "4",
+        "Alice",
+        "dragonfruit",
+        "fish",
+        "norwegian"
+      ],
+      [
+        "5",
         "Bob",
         "watermelon",
         "bird",
-        "swede"
-      ],
-      [
-        "5",
-        "Arnold",
-        "desert",
-        "dog",
-        "german"
+        "brit"
       ]
     ]
   }
